--- a/enhancements/test-files/14_Clash_pc0707_2026_Feb_swapped.xlsx
+++ b/enhancements/test-files/14_Clash_pc0707_2026_Feb_swapped.xlsx
@@ -420,99 +420,391 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Profit Center Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Profit Center Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Insurance Company Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Producer Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Policy Number</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Accounting Effective Date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Policy Effective Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Effective Date</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Amount (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Amount ($)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Accounting Effective Date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POL-0707-02000</t>
+          <t>Lima Office</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>707</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Global Assurance Corp</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pinnacle Agency Partners</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>POL-0707-02010</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>9077.530000000001</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1089.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>588.22</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="P2" t="n">
+        <v>501.08</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.5</v>
       </c>
-      <c r="C2" t="n">
+      <c r="R2" t="n">
         <v>200</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>46063</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POL-0707-02001</t>
+          <t>Lima Office</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>707</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Brown &amp; Brown</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>POL-0707-02011</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>18185.92</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2182.31</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1505.79</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P3" t="n">
+        <v>676.52</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="R3" t="n">
         <v>201</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>46064</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POL-0707-02002</t>
+          <t>Lima Office</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>707</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Heritage Casualty Co</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Brown &amp; Brown</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>POL-0707-02012</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>14772.37</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1772.68</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>921.79</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="P4" t="n">
+        <v>850.89</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="R4" t="n">
         <v>202</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>46065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POL-0707-02003</t>
+          <t>Lima Office</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>707</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Global Assurance Corp</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Apex Insurance Brokers</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>POL-0707-02013</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6006.12</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>720.73</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>389.19</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="P5" t="n">
+        <v>331.54</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" t="n">
+      <c r="R5" t="n">
         <v>203</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>46066</v>
       </c>
     </row>
   </sheetData>
